--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$G$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,8 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="74" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,7 +546,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prix et stocks volontairement absents : ils changent — à lire sur la page produit au moment de commander.  Colonne E (Qté) en jaune : à compléter, nombre entier, ex. 2.</t>
+          <t>Prix et stocks volontairement absents : ils changent — à lire sur la page produit au moment de commander.  Colonne E (Qté) en jaune : à compléter, nombre entier, ex. 2.  Colonne F : adresse en clair, à copier-coller.  Colonne G : cliquer sur « Ouvrir ».</t>
         </is>
       </c>
     </row>
@@ -577,7 +578,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Lien Mouser</t>
+          <t>Lien produit Mouser</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Recherche par référence</t>
         </is>
       </c>
     </row>
@@ -605,7 +611,12 @@
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>https://mouser.com/en/ProductDetail/Kycon/KPJX-4S-S</t>
+          <t>https://www.mouser.com/en/ProductDetail/Kycon/KPJX-4S-S?qs=0QDpPFt3C4bj8uE5yBzCJQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=KPJX-4S-S</t>
         </is>
       </c>
     </row>
@@ -633,7 +644,12 @@
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/ProductDetail/Kycon/KPJX-4S</t>
+          <t>https://www.mouser.fr/ProductDetail/Kycon/KPJX-4S?qs=PGF6ObTbUZ1PHc9As62%2FZQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=KPJX-4S</t>
         </is>
       </c>
     </row>
@@ -661,7 +677,12 @@
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPJX-PM-4S-S</t>
+          <t>https://www.mouser.com/ProductDetail/Kycon/KPJX-PM-4S-S?qs=zorda86t5M9ArIfKgei5Pg%3D%3D</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=KPJX-PM-4S-S</t>
         </is>
       </c>
     </row>
@@ -689,7 +710,12 @@
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPPX-4P</t>
+          <t>https://www.mouser.com/ProductDetail/Kycon/KPPX-4P?qs=Y0vc5luVLxJNKFay3ZyJLw%3D%3D</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
         </is>
       </c>
     </row>
@@ -717,7 +743,12 @@
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/490-SJ-43514</t>
+          <t>https://www.mouser.com/ProductDetail/Same-Sky/SJ-43514?qs=WyjlAZoYn51bsBOfuwwiuw%3D%3D</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=SJ-43514</t>
         </is>
       </c>
     </row>
@@ -745,7 +776,12 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/CUI-Devices/SJ-43514-SMT-TR/</t>
+          <t>https://www.mouser.com/ProductDetail/CUI-Devices/SJ-43514-SMT-TR/?qs=WyjlAZoYn528%252BiAb5RzVtg%3D%3D</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
         </is>
       </c>
     </row>
@@ -773,7 +809,12 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118193-0001LF</t>
+          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118193-0001LF?qs=Ywefl8B65e63Nsqd%2B8HZaQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
         </is>
       </c>
     </row>
@@ -801,7 +842,12 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118192-0001LF</t>
+          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118192-0001LF?qs=Ywefl8B65e5bHFoQtIudZg%3D%3D</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
         </is>
       </c>
     </row>
@@ -829,7 +875,12 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/en/ProductDetail/Amphenol-FCI/10118194-0001LF</t>
+          <t>https://www.mouser.com/en/ProductDetail/Amphenol-FCI/10118194-0001LF?qs=Ywefl8B65e4FIdY8OWfRQA%3D%3D</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
         </is>
       </c>
     </row>
@@ -857,7 +908,12 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>https://mouser.com/ProductDetail/Molex/54819-0519</t>
+          <t>https://www.mouser.com/ProductDetail/Molex/54819-0519?qs=x6EjVpvqMVObi%2BAAyuuEww%3D%3D</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=54819-0519</t>
         </is>
       </c>
     </row>
@@ -885,7 +941,12 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/GCT/USB4085-GF-A</t>
+          <t>https://www.mouser.com/ProductDetail/GCT/USB4085-GF-A?qs=KUoIvG%2F9Ilba1bQOahfWjw%3D%3D</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=USB4085-GF-A</t>
         </is>
       </c>
     </row>
@@ -916,6 +977,11 @@
           <t>https://www.mouser.com/new/bourns/bourns-mf-msmf-series-fuses/</t>
         </is>
       </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -944,6 +1010,11 @@
           <t>https://www.mouser.com/c/circuit-protection/thermistors/resettable-fuses-pptc/</t>
         </is>
       </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -969,7 +1040,12 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/PUI-Audio/AS01508MR-6-R</t>
+          <t>https://www.mouser.com/ProductDetail/PUI-Audio/AS01508MR-6-R?qs=vgjKjNJexThgIp5KgUGpgA%3D%3D</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=AS01508MR-6-R</t>
         </is>
       </c>
     </row>
@@ -1000,6 +1076,11 @@
           <t>https://www.mouser.com/en/c/electromechanical/audio-devices/speakers-transducers/</t>
         </is>
       </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1025,7 +1106,12 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Alps-Alpine/SKRPACE010</t>
+          <t>https://www.mouser.com/ProductDetail/Alps-Alpine/SKRPACE010?qs=dHDuPHwQO79W8iY66hDbLQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=SKRPACE010</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1139,12 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Omron-Electronics/B3F-1000</t>
+          <t>https://www.mouser.com/ProductDetail/Omron-Electronics/B3F-1000?qs=lK7M36XCk6JQHckSc1xIsg%3D%3D</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1172,12 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-VHETH</t>
+          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-VHETH?qs=pUKx8fyJudBCulCrBA9DxA%3D%3D</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1205,12 @@
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-JJB-ST</t>
+          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-JJB-ST?qs=K5ta8V%2BWhtbjRn899xwLFw%3D%3D</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1238,12 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>https://mouser.com/ProductDetail/Linx-Technologies/ANT-868-SP</t>
+          <t>https://www.mouser.com/ProductDetail/Linx-Technologies/ANT-868-SP?qs=K5ta8V%2BWhtYLcp%2FwdgtLaA%3D%3D</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
         </is>
       </c>
     </row>
@@ -1168,6 +1274,11 @@
           <t>https://www.mouser.com/c/passive-components/antennas/?center+frequency=868+MHz</t>
         </is>
       </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -1193,7 +1304,12 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/en/ProductDetail/Bourns/SRN4018-4R7M</t>
+          <t>https://www.mouser.com/en/ProductDetail/Bourns/SRN4018-4R7M?qs=UvjENeDOEed%2FCjy5nMh3Xg%3D%3D</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
         </is>
       </c>
     </row>
@@ -1224,6 +1340,11 @@
           <t>https://www.mouser.com/c/passive-components/capacitors/ceramic-capacitors/mlccs-smd-smt/</t>
         </is>
       </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -1252,6 +1373,11 @@
           <t>https://www.mouser.com/Passive-Components/Capacitors/Capacitor-Kits/_/N-2iq32</t>
         </is>
       </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1280,6 +1406,11 @@
           <t>https://www.mouser.com/c/passive-components/resistors/chip-smd-resistors/</t>
         </is>
       </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1308,6 +1439,11 @@
           <t>https://www.mouser.com/c/passive-components/resistors/resistor-kits/?termination+style=SMD%2FSMT</t>
         </is>
       </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1336,6 +1472,11 @@
           <t>https://www.mouser.com/en/c/power/batteries/nimh-nickel-metal-hydride-battery/?m=Panasonic</t>
         </is>
       </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=Panasonic+NiMH+AA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -1364,42 +1505,75 @@
           <t>https://www.mouser.com/c/semiconductors/embedded-processors-controllers/microcontrollers-mcu/?q=MSP430FR2</t>
         </is>
       </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F32"/>
+  <autoFilter ref="A4:G32"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$G$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -689,12 +689,12 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Fiche mâle d'accouplement (réfection du cordon)</t>
+          <t>Prise alimentation DIN puissance 4 contacts — série voisine KPJ, non blindée</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>KPPX-4P</t>
+          <t>KPJ-4S</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -704,332 +704,332 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Variante</t>
+          <t>À départager</t>
         </is>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPPX-4P?qs=Y0vc5luVLxJNKFay3ZyJLw%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Kycon/KPJ-4S?qs=/XicOQBKAMa%252BcJ0hGGZaig%3D%3D</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
+          <t>https://www.mouser.fr/c/?q=KPJ-4S</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Prise jack 3,5 mm, traversante</t>
+          <t>Prise alimentation DIN puissance 4 contacts — série voisine KPJ, blindée</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SJ-43514</t>
+          <t>KPJ-4S-S</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Same Sky (CUI Devices)</t>
+          <t>Kycon</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>À départager</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Same-Sky/SJ-43514?qs=WyjlAZoYn51bsBOfuwwiuw%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Kycon/KPJ-4S-S?qs=SrUfdAPSdgAPLkBk%2BStEGA%3D%3D</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SJ-43514</t>
+          <t>https://www.mouser.fr/c/?q=KPJ-4S-S</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Prise jack 3,5 mm, CMS</t>
+          <t>Prise alimentation DIN puissance 4 contacts — version haute température</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>SJ-43514-SMT-TR</t>
+          <t>KPJXHT-4S-S</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Same Sky (CUI Devices)</t>
+          <t>Kycon</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>Variante</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/CUI-Devices/SJ-43514-SMT-TR/?qs=WyjlAZoYn528%252BiAb5RzVtg%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Kycon/KPJXHT-4S-S?qs=6olcXJbp99TwdwXWG%2BzyAQ%3D%3D</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
+          <t>https://www.mouser.fr/c/?q=KPJXHT-4S-S</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Micro-USB B, CMS coudée</t>
+          <t>Fiche mâle d'accouplement (réfection du cordon)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10118193-0001LF</t>
+          <t>KPPX-4P</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Amphenol FCI</t>
+          <t>Kycon</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>Variante</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118193-0001LF?qs=Ywefl8B65e63Nsqd%2B8HZaQ%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Kycon/KPPX-4P?qs=Y0vc5luVLxJNKFay3ZyJLw%3D%3D</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
+          <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Micro-USB B, variante de montage</t>
+          <t>Prise jack 3,5 mm, traversante</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>10118192-0001LF</t>
+          <t>SJ-43514</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Amphenol FCI</t>
+          <t>Same Sky (CUI Devices)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Variante</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118192-0001LF?qs=Ywefl8B65e5bHFoQtIudZg%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Same-Sky/SJ-43514?qs=WyjlAZoYn51bsBOfuwwiuw%3D%3D</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
+          <t>https://www.mouser.fr/c/?q=SJ-43514</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Micro-USB B, variante de montage</t>
+          <t>Prise jack 3,5 mm, CMS</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10118194-0001LF</t>
+          <t>SJ-43514-SMT-TR</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Amphenol FCI</t>
+          <t>Same Sky (CUI Devices)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Variante</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/en/ProductDetail/Amphenol-FCI/10118194-0001LF?qs=Ywefl8B65e4FIdY8OWfRQA%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/CUI-Devices/SJ-43514-SMT-TR/?qs=WyjlAZoYn528%252BiAb5RzVtg%3D%3D</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
+          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Mini-USB B, 5 contacts</t>
+          <t>Micro-USB B, CMS coudée</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>54819-0519</t>
+          <t>10118193-0001LF</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Amphenol FCI</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Molex/54819-0519?qs=x6EjVpvqMVObi%2BAAyuuEww%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118193-0001LF?qs=Ywefl8B65e63Nsqd%2B8HZaQ%3D%3D</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=54819-0519</t>
+          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>USB-C, 16 contacts, traversante</t>
+          <t>Micro-USB B, variante de montage</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>USB4085-GF-A</t>
+          <t>10118192-0001LF</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>Amphenol FCI</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Variante</t>
         </is>
       </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/GCT/USB4085-GF-A?qs=KUoIvG%2F9Ilba1bQOahfWjw%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118192-0001LF?qs=Ywefl8B65e5bHFoQtIudZg%3D%3D</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=USB4085-GF-A</t>
+          <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Fusible réarmable PPTC, boîtier 1812</t>
+          <t>Micro-USB B, variante de montage</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>série MF-MSMF</t>
+          <t>10118194-0001LF</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>Amphenol FCI</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Variante</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/new/bourns/bourns-mf-msmf-series-fuses/</t>
+          <t>https://www.mouser.com/en/ProductDetail/Amphenol-FCI/10118194-0001LF?qs=Ywefl8B65e4FIdY8OWfRQA%3D%3D</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
+          <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Fusibles PPTC — catalogue complet</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mini-USB B, 5 contacts</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>54819-0519</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/c/circuit-protection/thermistors/resettable-fuses-pptc/</t>
+          <t>https://www.mouser.com/ProductDetail/Molex/54819-0519?qs=x6EjVpvqMVObi%2BAAyuuEww%3D%3D</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
+          <t>https://www.mouser.fr/c/?q=54819-0519</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Haut-parleur Ø15 mm, 8 Ω</t>
+          <t>USB-C, 16 contacts, traversante</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>AS01508MR-6-R</t>
+          <t>USB4085-GF-A</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>PUI Audio</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1040,95 +1040,95 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/PUI-Audio/AS01508MR-6-R?qs=vgjKjNJexThgIp5KgUGpgA%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/GCT/USB4085-GF-A?qs=KUoIvG%2F9Ilba1bQOahfWjw%3D%3D</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=AS01508MR-6-R</t>
+          <t>https://www.mouser.fr/c/?q=USB4085-GF-A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Haut-parleurs — catalogue</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Fusible réarmable PPTC, boîtier 1812</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>série MF-MSMF</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/en/c/electromechanical/audio-devices/speakers-transducers/</t>
+          <t>https://www.mouser.com/new/bourns/bourns-mf-msmf-series-fuses/</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
+          <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Bouton poussoir CMS (ceux de la carte)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>SKRPACE010</t>
+          <t>Fusibles PPTC — catalogue complet</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Alps Alpine</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Alps-Alpine/SKRPACE010?qs=dHDuPHwQO79W8iY66hDbLQ%3D%3D</t>
+          <t>https://www.mouser.com/c/circuit-protection/thermistors/resettable-fuses-pptc/</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SKRPACE010</t>
+          <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Bouton poussoir traversant 6 × 6 mm</t>
+          <t>Haut-parleur Ø15 mm, 8 Ω</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>B3F-1000</t>
+          <t>AS01508MR-6-R</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Omron</t>
+          <t>PUI Audio</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1139,217 +1139,217 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Omron-Electronics/B3F-1000?qs=lK7M36XCk6JQHckSc1xIsg%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/PUI-Audio/AS01508MR-6-R?qs=vgjKjNJexThgIp5KgUGpgA%3D%3D</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
+          <t>https://www.mouser.fr/c/?q=AS01508MR-6-R</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Antenne UHF hélicoïdale CMS</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>ANT-868-VHETH</t>
+          <t>Haut-parleurs — catalogue</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>TE / Linx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-VHETH?qs=pUKx8fyJudBCulCrBA9DxA%3D%3D</t>
+          <t>https://www.mouser.com/en/c/electromechanical/audio-devices/speakers-transducers/</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
+          <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Antenne UHF monopole embarqué Ø7 mm</t>
+          <t>Bouton poussoir CMS (ceux de la carte)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>ANT-868-JJB-ST</t>
+          <t>SKRPACE010</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>TE / Linx</t>
+          <t>Alps Alpine</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-JJB-ST?qs=K5ta8V%2BWhtbjRn899xwLFw%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Alps-Alpine/SKRPACE010?qs=dHDuPHwQO79W8iY66hDbLQ%3D%3D</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
+          <t>https://www.mouser.fr/c/?q=SKRPACE010</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Antenne UHF planaire CMS</t>
+          <t>Bouton poussoir traversant 6 × 6 mm</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>ANT-868-SP</t>
+          <t>B3F-1000</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>TE / Linx</t>
+          <t>Omron</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/ProductDetail/Linx-Technologies/ANT-868-SP?qs=K5ta8V%2BWhtYLcp%2FwdgtLaA%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/Omron-Electronics/B3F-1000?qs=lK7M36XCk6JQHckSc1xIsg%3D%3D</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
+          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Antennes 868 MHz — catalogue</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Antenne UHF hélicoïdale CMS</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>ANT-868-VHETH</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TE / Linx</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/c/passive-components/antennas/?center+frequency=868+MHz</t>
+          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-VHETH?qs=pUKx8fyJudBCulCrBA9DxA%3D%3D</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
+          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
+          <t>Antenne UHF monopole embarqué Ø7 mm</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>SRN4018-4R7M</t>
+          <t>ANT-868-JJB-ST</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>TE / Linx</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/en/ProductDetail/Bourns/SRN4018-4R7M?qs=UvjENeDOEed%2FCjy5nMh3Xg%3D%3D</t>
+          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-JJB-ST?qs=K5ta8V%2BWhtbjRn899xwLFw%3D%3D</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
+          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Condensateurs MLCC CMS — catalogue</t>
+          <t>Antenne UHF planaire CMS</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>0603 / 0805 / 1206</t>
+          <t>ANT-868-SP</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Murata, Yageo, KEMET</t>
+          <t>TE / Linx</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/c/passive-components/capacitors/ceramic-capacitors/mlccs-smd-smt/</t>
+          <t>https://www.mouser.com/ProductDetail/Linx-Technologies/ANT-868-SP?qs=K5ta8V%2BWhtYLcp%2FwdgtLaA%3D%3D</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
+          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Kits de condensateurs</t>
+          <t>Antennes 868 MHz — catalogue</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -1370,29 +1370,29 @@
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/Passive-Components/Capacitors/Capacitor-Kits/_/N-2iq32</t>
+          <t>https://www.mouser.com/c/passive-components/antennas/?center+frequency=868+MHz</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
+          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Résistances CMS — catalogue</t>
+          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>RC0805 / CRCW0805</t>
+          <t>SRN4018-4R7M</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Yageo, Vishay</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1403,116 +1403,215 @@
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/c/passive-components/resistors/chip-smd-resistors/</t>
+          <t>https://www.mouser.com/en/ProductDetail/Bourns/SRN4018-4R7M?qs=UvjENeDOEed%2FCjy5nMh3Xg%3D%3D</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
+          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Kits de résistances CMS</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Condensateurs MLCC CMS — catalogue</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>0603 / 0805 / 1206</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Murata, Yageo, KEMET</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/c/passive-components/resistors/resistor-kits/?termination+style=SMD%2FSMT</t>
+          <t>https://www.mouser.com/c/passive-components/capacitors/ceramic-capacitors/mlccs-smd-smt/</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
+          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Accus AA Ni-MH — la réparation la plus probable</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>gamme Ni-MH</t>
+          <t>Kits de condensateurs</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Prioritaire</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.com/en/c/power/batteries/nimh-nickel-metal-hydride-battery/?m=Panasonic</t>
+          <t>https://www.mouser.com/Passive-Components/Capacitors/Capacitor-Kits/_/N-2iq32</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=Panasonic+NiMH+AA</t>
+          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>MCU TI MSP430FR2xxx — famille</t>
+          <t>Résistances CMS — catalogue</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>réf. exacte à relire sur la puce</t>
+          <t>RC0805 / CRCW0805</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Yageo, Vishay</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.com/c/passive-components/resistors/chip-smd-resistors/</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Kits de résistances CMS</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.com/c/passive-components/resistors/resistor-kits/?termination+style=SMD%2FSMT</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Accus AA Ni-MH — la réparation la plus probable</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>gamme Ni-MH</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Panasonic</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Prioritaire</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.com/en/c/power/batteries/nimh-nickel-metal-hydride-battery/?m=Panasonic</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=Panasonic+NiMH+AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>MCU TI MSP430FR2xxx — famille</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>réf. exacte à relire sur la puce</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>À confirmer</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/c/semiconductors/embedded-processors-controllers/microcontrollers-mcu/?q=MSP430FR2</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G32"/>
+  <autoFilter ref="A4:G35"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -1574,6 +1673,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1807,7 +1912,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Diamètre extérieur de la bague en façade : ~12,9 mm avec corps ~15 × 17 mm → série KPJX ; ~9,5 mm → mini-DIN, autre famille limitée à ~1 A. Puis compter les trous côté cuivre : 4 contacts + 2 ergots + languette de masse → version blindée.</t>
+          <t>Plan de perçage constructeur à comparer trou par trou : https://www.mouser.com/datasheet/3/166/1/KPJX.pdf  —  Diamètre extérieur de la bague en façade : ~12,9 mm avec corps ~15 × 17 mm → série KPJX ; ~9,5 mm → mini-DIN, autre famille limitée à ~1 A. Puis compter les trous côté cuivre : 4 contacts + 2 ergots + languette de masse → version blindée.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -528,12 +528,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Lien produit Mouser</t>
+          <t>Recherche Mouser (lien fiable)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Recherche par référence</t>
+          <t>Fiche produit (si elle répond)</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=KPJX-4S-S</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/en/ProductDetail/Kycon/KPJX-4S-S?qs=0QDpPFt3C4bj8uE5yBzCJQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=KPJX-4S-S</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=KPJX-4S</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.fr/ProductDetail/Kycon/KPJX-4S?qs=PGF6ObTbUZ1PHc9As62%2FZQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=KPJX-4S</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=KPJX-PM-4S-S</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Kycon/KPJX-PM-4S-S?qs=zorda86t5M9ArIfKgei5Pg%3D%3D</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=KPJX-PM-4S-S</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=KPJ-4S</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Kycon/KPJ-4S?qs=/XicOQBKAMa%252BcJ0hGGZaig%3D%3D</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=KPJ-4S</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=KPJ-4S-S</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Kycon/KPJ-4S-S?qs=SrUfdAPSdgAPLkBk%2BStEGA%3D%3D</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=KPJ-4S-S</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=KPJXHT-4S-S</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Kycon/KPJXHT-4S-S?qs=6olcXJbp99TwdwXWG%2BzyAQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=KPJXHT-4S-S</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Kycon/KPPX-4P?qs=Y0vc5luVLxJNKFay3ZyJLw%3D%3D</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=SJ-43514</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Same-Sky/SJ-43514?qs=WyjlAZoYn51bsBOfuwwiuw%3D%3D</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=SJ-43514</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/CUI-Devices/SJ-43514-SMT-TR/?qs=WyjlAZoYn528%252BiAb5RzVtg%3D%3D</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118193-0001LF?qs=Ywefl8B65e63Nsqd%2B8HZaQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118192-0001LF?qs=Ywefl8B65e5bHFoQtIudZg%3D%3D</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/en/ProductDetail/Amphenol-FCI/10118194-0001LF?qs=Ywefl8B65e4FIdY8OWfRQA%3D%3D</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=54819-0519</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Molex/54819-0519?qs=x6EjVpvqMVObi%2BAAyuuEww%3D%3D</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=54819-0519</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=USB4085-GF-A</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/GCT/USB4085-GF-A?qs=KUoIvG%2F9Ilba1bQOahfWjw%3D%3D</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=USB4085-GF-A</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/new/bourns/bourns-mf-msmf-series-fuses/</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/c/circuit-protection/thermistors/resettable-fuses-pptc/</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=AS01508MR-6-R</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/PUI-Audio/AS01508MR-6-R?qs=vgjKjNJexThgIp5KgUGpgA%3D%3D</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=AS01508MR-6-R</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/en/c/electromechanical/audio-devices/speakers-transducers/</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=SKRPACE010</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Alps-Alpine/SKRPACE010?qs=dHDuPHwQO79W8iY66hDbLQ%3D%3D</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=SKRPACE010</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Omron-Electronics/B3F-1000?qs=lK7M36XCk6JQHckSc1xIsg%3D%3D</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-VHETH?qs=pUKx8fyJudBCulCrBA9DxA%3D%3D</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-JJB-ST?qs=K5ta8V%2BWhtbjRn899xwLFw%3D%3D</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/ProductDetail/Linx-Technologies/ANT-868-SP?qs=K5ta8V%2BWhtYLcp%2FwdgtLaA%3D%3D</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/c/passive-components/antennas/?center+frequency=868+MHz</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/en/ProductDetail/Bourns/SRN4018-4R7M?qs=UvjENeDOEed%2FCjy5nMh3Xg%3D%3D</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/c/passive-components/capacitors/ceramic-capacitors/mlccs-smd-smt/</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/Passive-Components/Capacitors/Capacitor-Kits/_/N-2iq32</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/c/passive-components/resistors/chip-smd-resistors/</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/c/passive-components/resistors/resistor-kits/?termination+style=SMD%2FSMT</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="12" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=Panasonic+NiMH+AA</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/en/c/power/batteries/nimh-nickel-metal-hydride-battery/?m=Panasonic</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=Panasonic+NiMH+AA</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
           <t>https://www.mouser.com/c/semiconductors/embedded-processors-controllers/microcontrollers-mcu/?q=MSP430FR2</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
         </is>
       </c>
     </row>

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -532,8 +532,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,12 +577,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Recherche Mouser (lien fiable)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Fiche produit (si elle répond)</t>
+          <t>Lien Mouser (recherche par référence)</t>
         </is>
       </c>
     </row>
@@ -614,11 +608,6 @@
           <t>https://www.mouser.fr/c/?q=KPJX-4S-S</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/en/ProductDetail/Kycon/KPJX-4S-S?qs=0QDpPFt3C4bj8uE5yBzCJQ%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -647,11 +636,6 @@
           <t>https://www.mouser.fr/c/?q=KPJX-4S</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/ProductDetail/Kycon/KPJX-4S?qs=PGF6ObTbUZ1PHc9As62%2FZQ%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -680,11 +664,6 @@
           <t>https://www.mouser.fr/c/?q=KPJX-PM-4S-S</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPJX-PM-4S-S?qs=zorda86t5M9ArIfKgei5Pg%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -713,11 +692,6 @@
           <t>https://www.mouser.fr/c/?q=KPJ-4S</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPJ-4S?qs=/XicOQBKAMa%252BcJ0hGGZaig%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -746,11 +720,6 @@
           <t>https://www.mouser.fr/c/?q=KPJ-4S-S</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPJ-4S-S?qs=SrUfdAPSdgAPLkBk%2BStEGA%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -779,11 +748,6 @@
           <t>https://www.mouser.fr/c/?q=KPJXHT-4S-S</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPJXHT-4S-S?qs=6olcXJbp99TwdwXWG%2BzyAQ%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -812,11 +776,6 @@
           <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Kycon/KPPX-4P?qs=Y0vc5luVLxJNKFay3ZyJLw%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -845,11 +804,6 @@
           <t>https://www.mouser.fr/c/?q=SJ-43514</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Same-Sky/SJ-43514?qs=WyjlAZoYn51bsBOfuwwiuw%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -878,11 +832,6 @@
           <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/CUI-Devices/SJ-43514-SMT-TR/?qs=WyjlAZoYn528%252BiAb5RzVtg%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -911,11 +860,6 @@
           <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118193-0001LF?qs=Ywefl8B65e63Nsqd%2B8HZaQ%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -944,11 +888,6 @@
           <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Amphenol-FCI/10118192-0001LF?qs=Ywefl8B65e5bHFoQtIudZg%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -977,11 +916,6 @@
           <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/en/ProductDetail/Amphenol-FCI/10118194-0001LF?qs=Ywefl8B65e4FIdY8OWfRQA%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1010,11 +944,6 @@
           <t>https://www.mouser.fr/c/?q=54819-0519</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Molex/54819-0519?qs=x6EjVpvqMVObi%2BAAyuuEww%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -1043,11 +972,6 @@
           <t>https://www.mouser.fr/c/?q=USB4085-GF-A</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/GCT/USB4085-GF-A?qs=KUoIvG%2F9Ilba1bQOahfWjw%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1076,11 +1000,6 @@
           <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/new/bourns/bourns-mf-msmf-series-fuses/</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1109,11 +1028,6 @@
           <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/c/circuit-protection/thermistors/resettable-fuses-pptc/</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1142,11 +1056,6 @@
           <t>https://www.mouser.fr/c/?q=AS01508MR-6-R</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/PUI-Audio/AS01508MR-6-R?qs=vgjKjNJexThgIp5KgUGpgA%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -1175,11 +1084,6 @@
           <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/en/c/electromechanical/audio-devices/speakers-transducers/</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1208,11 +1112,6 @@
           <t>https://www.mouser.fr/c/?q=SKRPACE010</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Alps-Alpine/SKRPACE010?qs=dHDuPHwQO79W8iY66hDbLQ%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1241,11 +1140,6 @@
           <t>https://www.mouser.fr/c/?q=B3F-1000</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Omron-Electronics/B3F-1000?qs=lK7M36XCk6JQHckSc1xIsg%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1274,11 +1168,6 @@
           <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-VHETH?qs=pUKx8fyJudBCulCrBA9DxA%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -1307,11 +1196,6 @@
           <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/TE-Connectivity-Linx-Technologies/ANT-868-JJB-ST?qs=K5ta8V%2BWhtbjRn899xwLFw%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1340,11 +1224,6 @@
           <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/ProductDetail/Linx-Technologies/ANT-868-SP?qs=K5ta8V%2BWhtYLcp%2FwdgtLaA%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -1373,11 +1252,6 @@
           <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/c/passive-components/antennas/?center+frequency=868+MHz</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1406,11 +1280,6 @@
           <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/en/ProductDetail/Bourns/SRN4018-4R7M?qs=UvjENeDOEed%2FCjy5nMh3Xg%3D%3D</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1439,11 +1308,6 @@
           <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/c/passive-components/capacitors/ceramic-capacitors/mlccs-smd-smt/</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1472,11 +1336,6 @@
           <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/Passive-Components/Capacitors/Capacitor-Kits/_/N-2iq32</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -1505,11 +1364,6 @@
           <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/c/passive-components/resistors/chip-smd-resistors/</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1538,11 +1392,6 @@
           <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/c/passive-components/resistors/resistor-kits/?termination+style=SMD%2FSMT</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -1571,11 +1420,6 @@
           <t>https://www.mouser.fr/c/?q=Panasonic+NiMH+AA</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/en/c/power/batteries/nimh-nickel-metal-hydride-battery/?m=Panasonic</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1604,81 +1448,45 @@
           <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.com/c/semiconductors/embedded-processors-controllers/microcontrollers-mcu/?q=MSP430FR2</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G35"/>
+  <autoFilter ref="A4:F35"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1088,12 +1088,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Bouton poussoir CMS (ceux de la carte)</t>
+          <t>Poussoir tactile CMS bas profil — série SKRW (corrigé par l'utilisateur)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKRPACE010</t>
+          <t>série SKRW</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1109,24 +1109,24 @@
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SKRPACE010</t>
+          <t>https://www.mouser.fr/c/?q=SKRW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Bouton poussoir traversant 6 × 6 mm</t>
+          <t>Poussoir tactile SKRW — variantes de durée de vie 50k / 500k / 1000k</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>B3F-1000</t>
+          <t>SKRWAEE030 · SKRWAME030 · SKRWADE030</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Omron</t>
+          <t>Alps Alpine</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1137,47 +1137,47 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
+          <t>https://www.mouser.fr/c/?q=SKRWAEE030</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Antenne UHF hélicoïdale CMS</t>
+          <t>Bouton poussoir traversant 6 × 6 mm</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ANT-868-VHETH</t>
+          <t>B3F-1000</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>TE / Linx</t>
+          <t>Omron</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
+          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Antenne UHF monopole embarqué Ø7 mm</t>
+          <t>Antenne UHF hélicoïdale CMS</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>ANT-868-JJB-ST</t>
+          <t>ANT-868-VHETH</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -1193,19 +1193,19 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
+          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Antenne UHF planaire CMS</t>
+          <t>Antenne UHF monopole embarqué Ø7 mm</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ANT-868-SP</t>
+          <t>ANT-868-JJB-ST</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1221,80 +1221,80 @@
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
+          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Antennes 868 MHz — catalogue</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Antenne UHF planaire CMS</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>ANT-868-SP</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TE / Linx</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
+          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>SRN4018-4R7M</t>
+          <t>Antennes 868 MHz — catalogue</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
+          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Condensateurs MLCC CMS — catalogue</t>
+          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>0603 / 0805 / 1206</t>
+          <t>SRN4018-4R7M</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Murata, Yageo, KEMET</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1305,152 +1305,180 @@
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
+          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Kits de condensateurs</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Condensateurs MLCC CMS — catalogue</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>0603 / 0805 / 1206</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Murata, Yageo, KEMET</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
+          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Résistances CMS — catalogue</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>RC0805 / CRCW0805</t>
+          <t>Kits de condensateurs</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Yageo, Vishay</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
+          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Kits de résistances CMS</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Résistances CMS — catalogue</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>RC0805 / CRCW0805</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yageo, Vishay</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
+          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Accus AA Ni-MH — la réparation la plus probable</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>gamme Ni-MH</t>
+          <t>Kits de résistances CMS</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Prioritaire</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=Panasonic+NiMH+AA</t>
+          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>MCU TI MSP430FR2xxx — famille</t>
+          <t>Batterie lithium plate (LiPo) — remplace les accus AA Ni-MH</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>réf. exacte à relire sur la puce</t>
+          <t>à relever sur la cellule</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Photo ext.</t>
         </is>
       </c>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=batterie+lithium+polymere+3.7V</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>MCU TI MSP430FR2xxx — famille</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>réf. exacte à relire sur la puce</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>À confirmer</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F35"/>
+  <autoFilter ref="A4:F36"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -1487,6 +1515,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1680,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1817,66 +1846,83 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Bouton poussoir</t>
+          <t>Bouton poussoir SKRW</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Hauteur de l'actionneur et force de contact.</t>
+          <t>Force d'actionnement et durée de vie visée (50k / 500k / 1000k cycles) — c'est le suffixe de la référence. Boîtier 3,7 × 3,7 mm, course 0,35 mm.</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Retrouver le même confort d'appui</t>
+          <t>Le suffixe exact de la référence SKRW</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Condensateurs / résistances</t>
+          <t>Batterie lithium plate</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Valeur, tolérance, tension de service, boîtier.</t>
+          <t>Longueur × largeur × épaisseur, capacité en mAh, tension nominale, type de connecteur, et présence ou non du circuit de protection intégré.</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sans ces cinq valeurs aucune cellule n'est commandable : une LiPo ne se substitue pas au jugé</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Écran LCD</t>
+          <t>Condensateurs / résistances</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Relever : nombre exact de broches, pas entre broches, dimensions du verre, et photo du verre allumé segment par segment. Le HT16C21 pilote au plus 20 segments × 4 communs — c'est la limite du plan à refaire.</t>
+          <t>Valeur, tolérance, tension de service, boîtier.</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Dossier de refabrication sur mesure, si le SAV ne fournit plus la pièce</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>Écran LCD</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Relever : nombre exact de broches, pas entre broches, dimensions du verre, et photo du verre allumé segment par segment. Le HT16C21 pilote au plus 20 segments × 4 communs — c'est la limite du plan à refaire.</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Dossier de refabrication sur mesure, si le SAV ne fournit plus la pièce</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
           <t>MCU MSP430FR2xxx</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Relire le marquage complet à la loupe. ⚠ Le MCU est programmé en usine : le remplacer ne remet pas l'appareil en service sans le firmware Linkx.</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Référence exacte</t>
         </is>
@@ -2002,7 +2048,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Le diagnostic de surchauffe place la chaîne piles Ni-MH / charge en tête des causes (hypothèses H1, H2 et H3).</t>
+          <t>⚠ OBSOLÈTE pour les appareils à batterie lithium plate. Le diagnostic de surchauffe repose sur la chimie Ni-MH (surcharge, absence de détection de fin de charge) : ces hypothèses H1, H2 et H3 ne s'appliquent PAS à une cellule lithium, dont la surchauffe relève du circuit de charge, du circuit de protection ou du gonflement de la cellule.</t>
         </is>
       </c>
     </row>

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -538,14 +538,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Liste Mouser — audioguide Tonwelt / Linkx TG-288 et sa valise de charge</t>
+          <t>Liste Mouser — audioguide Tonwelt / Linkx et sa valise de charge</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prix et stocks volontairement absents : ils changent — à lire sur la page produit au moment de commander.  Colonne E (Qté) en jaune : à compléter, nombre entier, ex. 2.  Colonne F : adresse en clair, à copier-coller.  Colonne G : cliquer sur « Ouvrir ».</t>
+          <t>Liste arrêtée par l'utilisateur (16 lignes retenues sur 31), plus les poussoirs SKRW et la batterie lithium.  Prix et stocks absents : ils changent.  Colonne E (Qté) en jaune : à compléter, nombre entier, ex. 2.  Colonne F : adresse en clair, à copier-coller.  Colonne G : cliquer sur « Ouvrir ».</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Prise alimentation DIN puissance 4 contacts, non blindée</t>
+          <t>Fiche mâle d'accouplement (réfection du cordon)</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>KPJX-4S</t>
+          <t>KPPX-4P</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -633,108 +633,108 @@
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=KPJX-4S</t>
+          <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Prise alimentation, montage sur panneau</t>
+          <t>Prise jack 3,5 mm, CMS</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>KPJX-PM-4S-S</t>
+          <t>SJ-43514-SMT-TR</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Kycon</t>
+          <t>Same Sky (CUI Devices)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Variante</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=KPJX-PM-4S-S</t>
+          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Prise alimentation DIN puissance 4 contacts — série voisine KPJ, non blindée</t>
+          <t>Micro-USB B, CMS coudée</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>KPJ-4S</t>
+          <t>10118193-0001LF</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Kycon</t>
+          <t>Amphenol FCI</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>À départager</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=KPJ-4S</t>
+          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Prise alimentation DIN puissance 4 contacts — série voisine KPJ, blindée</t>
+          <t>Micro-USB B, variante de montage</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>KPJ-4S-S</t>
+          <t>10118192-0001LF</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Kycon</t>
+          <t>Amphenol FCI</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>À départager</t>
+          <t>Variante</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=KPJ-4S-S</t>
+          <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Prise alimentation DIN puissance 4 contacts — version haute température</t>
+          <t>Micro-USB B, variante de montage</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>KPJXHT-4S-S</t>
+          <t>10118194-0001LF</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Kycon</t>
+          <t>Amphenol FCI</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -745,322 +745,322 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=KPJXHT-4S-S</t>
+          <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Fiche mâle d'accouplement (réfection du cordon)</t>
+          <t>Mini-USB B, 5 contacts</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>KPPX-4P</t>
+          <t>54819-0519</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Kycon</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Variante</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=KPPX-4P</t>
+          <t>https://www.mouser.fr/c/?q=54819-0519</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Prise jack 3,5 mm, traversante</t>
+          <t>Poussoir tactile CMS bas profil — série SKRW</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>SJ-43514</t>
+          <t>série SKRW</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Same Sky (CUI Devices)</t>
+          <t>Alps Alpine</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SJ-43514</t>
+          <t>https://www.mouser.fr/fr/new/alps-alpine/alps-alpine-skrw-tact-switches/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Prise jack 3,5 mm, CMS</t>
+          <t>Poussoir SKRW — variantes 50k / 500k / 1000k cycles</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>SJ-43514-SMT-TR</t>
+          <t>SKRWAEE030 · SKRWAME030 · SKRWADE030</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Same Sky (CUI Devices)</t>
+          <t>Alps Alpine</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
+          <t>https://www.mouser.fr/c/?q=SKRW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Micro-USB B, CMS coudée</t>
+          <t>Fusible réarmable PPTC, boîtier 1812</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>10118193-0001LF</t>
+          <t>série MF-MSMF</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Amphenol FCI</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Documenté</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
+          <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Micro-USB B, variante de montage</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>10118192-0001LF</t>
+          <t>Fusibles PPTC — catalogue complet</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Amphenol FCI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Variante</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=10118192-0001LF</t>
+          <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Micro-USB B, variante de montage</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>10118194-0001LF</t>
+          <t>Haut-parleurs — catalogue</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Amphenol FCI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Variante</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=10118194-0001LF</t>
+          <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mini-USB B, 5 contacts</t>
+          <t>Antenne UHF hélicoïdale CMS</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>54819-0519</t>
+          <t>ANT-868-VHETH</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>TE / Linx</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Documenté</t>
         </is>
       </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=54819-0519</t>
+          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>USB-C, 16 contacts, traversante</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>USB4085-GF-A</t>
+          <t>Antennes 868 MHz — catalogue</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=USB4085-GF-A</t>
+          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Fusible réarmable PPTC, boîtier 1812</t>
+          <t>Batterie lithium plate (LiPo) — remplace les accus Ni-MH</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>série MF-MSMF</t>
+          <t>à relever sur la cellule</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Photo ext.</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=MF-MSMF</t>
+          <t>https://www.mouser.fr/c/?q=3.7V+Lipo+Battery</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Fusibles PPTC — catalogue complet</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>SRN4018-4R7M</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=fusible+PPTC+1812</t>
+          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Haut-parleur Ø15 mm, 8 Ω</t>
+          <t>Condensateurs MLCC CMS — catalogue</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>AS01508MR-6-R</t>
+          <t>0603 / 0805 / 1206</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>PUI Audio</t>
+          <t>Murata, Yageo, KEMET</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=AS01508MR-6-R</t>
+          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Haut-parleurs — catalogue</t>
+          <t>Kits de résistances CMS</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -1081,404 +1081,40 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=haut-parleur+15mm+8+ohm</t>
+          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Poussoir tactile CMS bas profil — série SKRW (corrigé par l'utilisateur)</t>
+          <t>MCU TI MSP430FR2xxx — famille</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>série SKRW</t>
+          <t>réf. exacte à relire sur la puce</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Alps Alpine</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SKRW</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Poussoir tactile SKRW — variantes de durée de vie 50k / 500k / 1000k</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>SKRWAEE030 · SKRWAME030 · SKRWADE030</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Alps Alpine</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>À confirmer</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=SKRWAEE030</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Bouton poussoir traversant 6 × 6 mm</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>B3F-1000</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Omron</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>À confirmer</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=B3F-1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Antenne UHF hélicoïdale CMS</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>ANT-868-VHETH</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>TE / Linx</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Documenté</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-VHETH</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Antenne UHF monopole embarqué Ø7 mm</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>ANT-868-JJB-ST</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>TE / Linx</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Documenté</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-JJB-ST</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Antenne UHF planaire CMS</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>ANT-868-SP</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>TE / Linx</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Documenté</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=ANT-868-SP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Antennes 868 MHz — catalogue</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=antenne+868+MHz</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>SRN4018-4R7M</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Bourns</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Vu</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Condensateurs MLCC CMS — catalogue</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>0603 / 0805 / 1206</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Murata, Yageo, KEMET</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Vu</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Kits de condensateurs</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Catalogue</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=capacitor+kit</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Résistances CMS — catalogue</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>RC0805 / CRCW0805</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Yageo, Vishay</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Vu</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=RC0805+resistance</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Kits de résistances CMS</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Catalogue</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Batterie lithium plate (LiPo) — remplace les accus AA Ni-MH</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>à relever sur la cellule</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Photo ext.</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=batterie+lithium+polymere+3.7V</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>MCU TI MSP430FR2xxx — famille</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>réf. exacte à relire sur la puce</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>À confirmer</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
           <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F36"/>
+  <autoFilter ref="A4:F23"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -1503,19 +1139,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -976,22 +976,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Batterie lithium plate (LiPo) — remplace les accus Ni-MH</t>
+          <t>Batterie lithium plate — cellule relevée n°1 (carte à ressort d'antenne)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>à relever sur la cellule</t>
+          <t>JHY632570 · 3,7 V · 1300 mAh · 6,3×25×70 mm</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JHY</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Photo ext.</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E19" s="7" t="n"/>
@@ -1004,17 +1004,17 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
+          <t>Batterie lithium plate — cellule relevée n°2 (carte Eco 2.0, USB-C)</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>SRN4018-4R7M</t>
+          <t>sans référence · 3,87 V · 1000 mAh</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1025,24 +1025,24 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
+          <t>https://www.mouser.fr/c/?q=3.8V+Lipo+Battery</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Condensateurs MLCC CMS — catalogue</t>
+          <t>Batterie lithium plate — cellule relevée n°4</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>0603 / 0805 / 1206</t>
+          <t>LIDIO 355485 · 3,8 V · 2500 mAh · 3,5×54×85 mm</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Murata, Yageo, KEMET</t>
+          <t>LIDIO</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1053,68 +1053,152 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
+          <t>https://www.mouser.fr/c/?q=3.8V+Lipo+Battery</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Kits de résistances CMS</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
+          <t>⚠ Aucune de ces cellules n'est distribuée par Mouser — voir docs/batteries-lithium-tonwelt.md</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>JHY et LIDIO = fabricants OEM</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Hors Mouser</t>
         </is>
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
+          <t>https://www.mouser.fr/c/?q=lithium+polymer+battery+pack</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>MCU TI MSP430FR2xxx — famille</t>
+          <t>Inductance blindée 4,7 µH, 4×4 mm (étage boost)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>réf. exacte à relire sur la puce</t>
+          <t>SRN4018-4R7M</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
+          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Condensateurs MLCC CMS — catalogue</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>0603 / 0805 / 1206</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Murata, Yageo, KEMET</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Kits de résistances CMS</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=resistor+kit+0805</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>MCU TI MSP430FR2xxx — famille</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>réf. exacte à relire sur la puce</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>À confirmer</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
           <t>https://www.mouser.fr/c/?q=MSP430FR2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F23"/>
+  <autoFilter ref="A4:F26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -1139,6 +1223,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Hors Mouser" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Mesures restantes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="tourGuide AIR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$26</definedName>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,12 @@
       <color rgb="000563C1"/>
       <sz val="9"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -113,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +166,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1784,4 +1798,414 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tourGuide AIR — le seul produit touché par la panne de surchauffe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sous-ensemble de la feuille « Liste Mouser », restreint à ce qui est constaté ou attesté sur la carte du tourGuide AIR (les 15 photos macro de diagnostics/talkie-surchauffe/). La feuille principale reste inchangée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Composant</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Référence</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi cette ligne</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Lien Mouser</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cellule lithium plate</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>JHY632570 · 3,7 V · 1300 mAh</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Carte à ressort d'antenne + micro-USB — ⚠ reste à confirmer que cette carte est bien l'AIR</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=3.7V+Lipo+Battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Port de charge micro-USB B</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>10118193-0001LF (+ variantes …192 / …194)</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Documenté</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Le diagnostic cite le port micro-USB (§6.7, corrosion fréquente en location)</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=10118193-0001LF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Poussoirs tactiles CMS</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>série SKRW</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Corrigé par l'utilisateur. Suffixe selon durée de vie visée</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=SKRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Inductance blindée 4,7 µH, 4×4 mm</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>SRN4018-4R7M</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Deux étages à découpage sur la carte</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=SRN4018-4R7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Condensateurs MLCC 0603 / 0805</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>à relever</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>473 = 47 nF identifié sur l'étage boost</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=MLCC+0805</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Résistances 0805</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>à relever</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>3R3 = 3,3 Ω identifié</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=RC0805</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Prise jack 3,5 mm (sortie casque)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SJ-43514-SMT-TR</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Documenté</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Fiche Linkx : sortie casque sur la version récepteur</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=SJ-43514-SMT-TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Écran LCD à segments</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>SUR MESURE — hors catalogue</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Vu</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Pictogrammes propres au produit. SAV Linkx/Tonwelt ou refabrication sur plan</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Prise d'alimentation de la VALISE de charge</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>KPJX-4S-S</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Photo ext.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Appartient à la valise, pas à l'appareil — mais la valise est suspecte n°4</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=KPJX-4S-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Volontairement EXCLU du périmètre AIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Écarté</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>USB-C et nappe FPC</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ce sont les connecteurs de la carte « Eco 2.0 » (supraGuide ECO), pas de l'AIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Antennes Linx ANT-868-*</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>L'AIR porte un ressort d'antenne soudé sur la carte, pas une antenne de catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Prise mini-USB</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Gardée par l'utilisateur, mais non constatée sur la carte de l'AIR — appartient à un autre produit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Haut-parleur</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Non constaté sur l'AIR : c'est un récepteur à écouteurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Fusible PPTC</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Non constaté sur les photos de l'AIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>MCU, SoC RF, driver LCD, TCXO, 4 codes CMS non résolus</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Voir la feuille « Hors Mouser » : non commandables ou non identifiés</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId8"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Mesures restantes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sources &amp; statuts" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="tourGuide AIR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Batteries" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Liste Mouser'!$A$4:$F$26</definedName>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +70,18 @@
       <b val="1"/>
       <color rgb="00E65100"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -120,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,6 +186,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2208,4 +2231,341 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Batteries lithium plates — recherche Mouser ciblée par cellule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Codes à six chiffres = épaisseur (dixièmes de mm) · largeur · longueur. Aucune des trois cellules d'origine n'est distribuée par Mouser : ce sont des cellules OEM. Les recherches ci-dessous visent un ÉQUIVALENT, pas la référence d'origine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Cellule d'origine</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Marquage</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Spécification relevée</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ce qu'il faut chercher</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Recherche Mouser</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cellule n°1 — carte à ressort d'antenne (tourGuide AIR probable)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>JHY632570</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>3,7 V · 1300 mAh · 4,81 Wh · 6,3 × 25 × 70 mm</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Chercher : LiPo 3,7 V, 1200–1500 mAh, épaisseur ≤ 6,5 mm, avec circuit de protection et connecteur</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=LiPo+1300mAh+3.7V</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Cellule n°2 — carte Eco 2.0 (supraGuide ECO)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>sans référence</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>3,87 V · 1000 mAh · dimensions à mesurer</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>⚠ 3,87 V = LiPo HAUTE TENSION (charge 4,35 V). Le filtre Mouser ne propose que du 3,7 V : équivalent peu probable en catalogue</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=LiPo+1000mAh</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Cellule n°4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>LIDIO 355485</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>3,8 V · 2500 mAh · 9,5 Wh · 3,5 × 54 × 85 mm</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>⚠ 3,8 V = haute tension également. Chercher 2000–2600 mAh, épaisseur ≤ 4 mm</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=LiPo+2500mAh</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Cellule n°3</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>illisible sur la photo</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>3,8 V à confirmer</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Refaire une photo nette du marquage avant toute recherche</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Familles et sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Packs LiPo — catalogue complet</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Le point d'entrée général, à filtrer par tension, capacité et connecteur</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=3.7V+Lipo+Battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Packs LiPo à connecteur JST</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Vos cellules sortent sur un JST 2 points, fil rouge et noir</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=lithium+polymer+battery+pack+JST</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Jauch Quartz, série LP — chez DIGIKEY, pas Mouser</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Le meilleur équivalent industriel : même convention de code à six chiffres (LP + TTWWLL), 60 à 6000 mAh, 3,7 V / charge 4,2 V. Non distribué par Mouser</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>https://www.digikey.fr/fr/products/filter/batteries-rechargeable-secondary/91?s=jauch</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Les cinq critères d'un équivalent — aucun n'est facultatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>1. Dimensions</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Épaisseur × largeur × longueur MESURÉES au pied à coulisse — le code à six chiffres est une convention, pas une garantie</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2. Capacité</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>En mAh. Une capacité supérieure allonge l'autonomie mais souvent l'épaisseur aussi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>3. Tension nominale</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>⚠ LE CRITÈRE CRITIQUE. 3,7 V (charge 4,20 V) et 3,8/3,87 V (charge 4,35 V) ne sont PAS interchangeables. Une 3,7 V dans un chargeur 4,35 V est en surcharge permanente : elle chauffe et gonfle</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>4. Circuit de protection</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Vos cellules en ont un, visible sous le kapton jaune. Une cellule nue sans protection est dangereuse dans cet appareil</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>5. Connecteur et POLARITÉ</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>JST 2 points. La polarité n'est pas normalisée sur les cellules chinoises : vérifier au voltmètre AVANT de brancher, sous peine de détruire la carte</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>🔥 Sécurité : une poche lithium gonflée ou en surchauffe est un risque d'incendie. Ne pas la percer, ne pas la plier, ne pas continuer à la charger. La sortir de l'appareil, la placer dans un contenant ininflammable, la faire reprendre en déchet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -575,7 +575,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Liste Mouser — audioguide Tonwelt / Linkx et sa valise de charge</t>
+          <t>Liste Mouser - audioguide Tonwelt / Linkx et sa valise de charge</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Poussoir tactile CMS bas profil — série SKRW</t>
+          <t>Poussoir tactile CMS bas profil - série SKRW</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Poussoir SKRW — variantes 50k / 500k / 1000k cycles</t>
+          <t>Poussoir SKRW - variantes 50k / 500k / 1000k cycles</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Fusibles PPTC — catalogue complet</t>
+          <t>Fusibles PPTC - catalogue complet</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -929,17 +929,17 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Haut-parleurs — catalogue</t>
+          <t>Haut-parleurs - catalogue</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Antennes 868 MHz — catalogue</t>
+          <t>Antennes 868 MHz - catalogue</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Batterie lithium plate — cellule relevée n°1 (carte à ressort d'antenne)</t>
+          <t>Batterie lithium plate - cellule relevée n°1 (carte à ressort d'antenne)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Batterie lithium plate — cellule relevée n°2 (carte Eco 2.0, USB-C)</t>
+          <t>Batterie lithium plate - cellule relevée n°2 (carte Eco 2.0, USB-C)</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Batterie lithium plate — cellule relevée n°4</t>
+          <t>Batterie lithium plate - cellule relevée n°4</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>⚠ Aucune de ces cellules n'est distribuée par Mouser — voir docs/batteries-lithium-tonwelt.md</t>
+          <t>Attention : Aucune de ces cellules n'est distribuée par Mouser - voir docs/batteries-lithium-tonwelt.md</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Condensateurs MLCC CMS — catalogue</t>
+          <t>Condensateurs MLCC CMS - catalogue</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>MCU TI MSP430FR2xxx — famille</t>
+          <t>MCU TI MSP430FR2xxx - famille</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>TCXO « 24.04 AK AD » — 24,04 MHz</t>
+          <t>TCXO « 24.04 AK AD » - 24,04 MHz</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>« 19AKM » — SOT-23-5, convertisseur boost</t>
+          <t>« 19AKM » - SOT-23-5, convertisseur boost</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1394,7 +1394,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>« CDV 221 A5L2 » — SOP-8</t>
+          <t>« CDV 221 A5L2 » - SOP-8</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>« 724 2G SU » — SOP-8</t>
+          <t>« 724 2G SU » - SOP-8</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>« BSG· TI 8A8 A46R » — QFN-16</t>
+          <t>« BSG· TI 8A8 A46R » - QFN-16</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Plan de perçage constructeur à comparer trou par trou : https://www.mouser.com/datasheet/3/166/1/KPJX.pdf  —  Diamètre extérieur de la bague en façade : ~12,9 mm avec corps ~15 × 17 mm → série KPJX ; ~9,5 mm → mini-DIN, autre famille limitée à ~1 A. Puis compter les trous côté cuivre : 4 contacts + 2 ergots + languette de masse → version blindée.</t>
+          <t>Plan de perçage constructeur à comparer trou par trou : https://www.mouser.com/datasheet/3/166/1/KPJX.pdf  -  Diamètre extérieur de la bague en façade : ~12,9 mm avec corps ~15 × 17 mm → série KPJX ; ~9,5 mm → mini-DIN, autre famille limitée à ~1 A. Puis compter les trous côté cuivre : 4 contacts + 2 ergots + languette de masse → version blindée.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>La bande réelle : 863–865 MHz (Europe) ou 902–928 MHz (US). Elle est sur l'étiquette de l'appareil.</t>
+          <t>La bande réelle : 863-865 MHz (Europe) ou 902-928 MHz (US). Elle est sur l'étiquette de l'appareil.</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Force d'actionnement et durée de vie visée (50k / 500k / 1000k cycles) — c'est le suffixe de la référence. Boîtier 3,7 × 3,7 mm, course 0,35 mm.</t>
+          <t>Force d'actionnement et durée de vie visée (50k / 500k / 1000k cycles) - c'est le suffixe de la référence. Boîtier 3,7 × 3,7 mm, course 0,35 mm.</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Relever : nombre exact de broches, pas entre broches, dimensions du verre, et photo du verre allumé segment par segment. Le HT16C21 pilote au plus 20 segments × 4 communs — c'est la limite du plan à refaire.</t>
+          <t>Relever : nombre exact de broches, pas entre broches, dimensions du verre, et photo du verre allumé segment par segment. Le HT16C21 pilote au plus 20 segments × 4 communs - c'est la limite du plan à refaire.</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Relire le marquage complet à la loupe. ⚠ Le MCU est programmé en usine : le remplacer ne remet pas l'appareil en service sans le firmware Linkx.</t>
+          <t>Relire le marquage complet à la loupe. Attention : Le MCU est programmé en usine : le remplacer ne remet pas l'appareil en service sans le firmware Linkx.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ni photographié ni documenté ici. La référence est un point de départ catalogue — voir l'onglet « Mesures restantes ».</t>
+          <t>Ni photographié ni documenté ici. La référence est un point de départ catalogue - voir l'onglet « Mesures restantes ».</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>⚠ OBSOLÈTE pour les appareils à batterie lithium plate. Le diagnostic de surchauffe repose sur la chimie Ni-MH (surcharge, absence de détection de fin de charge) : ces hypothèses H1, H2 et H3 ne s'appliquent PAS à une cellule lithium, dont la surchauffe relève du circuit de charge, du circuit de protection ou du gonflement de la cellule.</t>
+          <t>Attention : OBSOLÈTE pour les appareils à batterie lithium plate. Le diagnostic de surchauffe repose sur la chimie Ni-MH (surcharge, absence de détection de fin de charge) : ces hypothèses H1, H2 et H3 ne s'appliquent PAS à une cellule lithium, dont la surchauffe relève du circuit de charge, du circuit de protection ou du gonflement de la cellule.</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>L'alimentation associée à la prise Kycon est donnée pour 5 V / 10 A / 50 W : c'est le format d'une valise de charge multi-emplacements, pas d'un audioguide qui se charge en micro-USB sur 2 × AA Ni-MH. Or le diagnostic désigne la valise de charge comme suspect à tester. Si cette prise est celle de la valise, les deux sujets n'en font qu'un — et changer le connecteur ne réglera pas la surchauffe.</t>
+          <t>L'alimentation associée à la prise Kycon est donnée pour 5 V / 10 A / 50 W : c'est le format d'une valise de charge multi-emplacements, pas d'un audioguide qui se charge en micro-USB sur 2 × AA Ni-MH. Or le diagnostic désigne la valise de charge comme suspect à tester. Si cette prise est celle de la valise, les deux sujets n'en font qu'un - et changer le connecteur ne réglera pas la surchauffe.</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>tourGuide AIR — le seul produit touché par la panne de surchauffe</t>
+          <t>tourGuide AIR - le seul produit touché par la panne de surchauffe</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Carte à ressort d'antenne + micro-USB — ⚠ reste à confirmer que cette carte est bien l'AIR</t>
+          <t>Carte à ressort d'antenne + micro-USB - Attention : reste à confirmer que cette carte est bien l'AIR</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>SUR MESURE — hors catalogue</t>
+          <t>SUR MESURE - hors catalogue</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Appartient à la valise, pas à l'appareil — mais la valise est suspecte n°4</t>
+          <t>Appartient à la valise, pas à l'appareil - mais la valise est suspecte n°4</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Gardée par l'utilisateur, mais non constatée sur la carte de l'AIR — appartient à un autre produit</t>
+          <t>Gardée par l'utilisateur, mais non constatée sur la carte de l'AIR - appartient à un autre produit</t>
         </is>
       </c>
     </row>
@@ -2239,20 +2239,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Batteries lithium plates — recherche Mouser ciblée par cellule</t>
+          <t>Batteries lithium plates - recherche Mouser ciblée par cellule</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Cellule n°1 — carte à ressort d'antenne (tourGuide AIR probable)</t>
+          <t>Cellule n°1 - carte à ressort d'antenne (tourGuide AIR probable)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Chercher : LiPo 3,7 V, 1200–1500 mAh, épaisseur ≤ 6,5 mm, avec circuit de protection et connecteur</t>
+          <t>Chercher : LiPo 3,7 V, 1200-1500 mAh, épaisseur ≤ 6,5 mm, avec circuit de protection et connecteur</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Cellule n°2 — carte Eco 2.0 (supraGuide ECO)</t>
+          <t>Cellule n°2 - carte Eco 2.0 (supraGuide ECO)</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>⚠ 3,87 V = LiPo HAUTE TENSION (charge 4,35 V). Le filtre Mouser ne propose que du 3,7 V : équivalent peu probable en catalogue</t>
+          <t>Attention : 3,87 V = LiPo HAUTE TENSION (charge 4,35 V). Le filtre Mouser ne propose que du 3,7 V : équivalent peu probable en catalogue</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>⚠ 3,8 V = haute tension également. Chercher 2000–2600 mAh, épaisseur ≤ 4 mm</t>
+          <t>Attention : 3,8 V = haute tension également. Chercher 2000-2600 mAh, épaisseur ≤ 4 mm</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -2394,29 +2394,34 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Familles et sources</t>
+          <t>Ou chercher un equivalent, site par site</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Famille</t>
+          <t>Site</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>Quoi</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>Pourquoi</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lien</t>
         </is>
@@ -2425,146 +2430,253 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Packs LiPo — catalogue complet</t>
+          <t>DigiKey</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Le point d'entrée général, à filtrer par tension, capacité et connecteur</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=3.7V+Lipo+Battery</t>
+          <t>Jauch Quartz, serie LP</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Le meilleur equivalent industriel. Meme convention de code a six chiffres, vendu avec circuit de protection et fils (PCM + 2 WIRES 50MM). Tension 3,7 V, charge 4,20 V. Non distribue par Mouser.</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/product-highlight/j/jauch-quartz/lithium-polymer-batteries</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Packs LiPo à connecteur JST</t>
+          <t>DigiKey</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Vos cellules sortent sur un JST 2 points, fil rouge et noir</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>https://www.mouser.fr/c/?q=lithium+polymer+battery+pack+JST</t>
+          <t>Exemple : LP503562JU</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Format 5,0 x 35 x 62 mm, avec PCM et fils. Sert de modele pour comprendre la designation.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/jauch-quartz/LP503562JU/9560989</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Jauch Quartz, série LP — chez DIGIKEY, pas Mouser</t>
+          <t>DigiKey</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Le meilleur équivalent industriel : même convention de code à six chiffres (LP + TTWWLL), 60 à 6000 mAh, 3,7 V / charge 4,2 V. Non distribué par Mouser</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>https://www.digikey.fr/fr/products/filter/batteries-rechargeable-secondary/91?s=jauch</t>
+          <t>Exemple : LP561836JU</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Format 5,6 x 18 x 36 mm, 350 mAh, avec PCM et fils.</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/jauch-quartz/LP561836JU-PCM-2-WIRES-50MM/9560979</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>DigiKey</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Catalogue packs lithium polymere</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>A filtrer par capacite et dimensions.</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/filter/battery-packs/lithium-polymer/89</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Les cinq critères d'un équivalent — aucun n'est facultatif</t>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>EEMB (direct ou Amazon.fr)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Cellules poche a code de taille</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Le plus proche de vos cellules OEM : meme logique de code (602835, 603449, 103395), livrees avec connecteur JST et circuit de protection. Fabricant chinois etabli, vendu au detail en Europe.</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>https://www.eemb.com/categories-55</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>1. Dimensions</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Épaisseur × largeur × longueur MESURÉES au pied à coulisse — le code à six chiffres est une convention, pas une garantie</t>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>TYVA Energie (France)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Fabrication sur mesure</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Si aucun format standard ne convient, ou pour une cellule haute tension introuvable en catalogue.</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>https://tyva-energie.com/en/custom-lithium-battery-manufacturer/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>2. Capacité</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>En mAh. Une capacité supérieure allonge l'autonomie mais souvent l'épaisseur aussi</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>3. Tension nominale</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>⚠ LE CRITÈRE CRITIQUE. 3,7 V (charge 4,20 V) et 3,8/3,87 V (charge 4,35 V) ne sont PAS interchangeables. Une 3,7 V dans un chargeur 4,35 V est en surcharge permanente : elle chauffe et gonfle</t>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Mouser</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Packs LiPo 3,7 V</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Catalogue generaliste, sans recherche par code de taille. Ne propose que du 3,7 V.</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>https://www.mouser.fr/c/?q=3.7V+Lipo+Battery</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>4. Circuit de protection</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Vos cellules en ont un, visible sous le kapton jaune. Une cellule nue sans protection est dangereuse dans cet appareil</t>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Les cinq critères d'un équivalent - aucun n'est facultatif</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
+          <t>1. Dimensions</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Épaisseur × largeur × longueur MESURÉES au pied à coulisse - le code à six chiffres est une convention, pas une garantie</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>2. Capacité</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>En mAh. Une capacité supérieure allonge l'autonomie mais souvent l'épaisseur aussi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>3. Tension nominale</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Attention : LE CRITÈRE CRITIQUE. 3,7 V (charge 4,20 V) et 3,8/3,87 V (charge 4,35 V) ne sont PAS interchangeables. Une 3,7 V dans un chargeur 4,35 V est en surcharge permanente : elle chauffe et gonfle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>4. Circuit de protection</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Vos cellules en ont un, visible sous le kapton jaune. Une cellule nue sans protection est dangereuse dans cet appareil</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
           <t>5. Connecteur et POLARITÉ</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>JST 2 points. La polarité n'est pas normalisée sur les cellules chinoises : vérifier au voltmètre AVANT de brancher, sous peine de détruire la carte</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>🔥 Sécurité : une poche lithium gonflée ou en surchauffe est un risque d'incendie. Ne pas la percer, ne pas la plier, ne pas continuer à la charger. La sortir de l'appareil, la placer dans un contenant ininflammable, la faire reprendre en déchet.</t>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Sécurité : Sécurité : une poche lithium gonflée ou en surchauffe est un risque d'incendie. Ne pas la percer, ne pas la plier, ne pas continuer à la charger. La sortir de l'appareil, la placer dans un contenant ininflammable, la faire reprendre en déchet.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B23:E23"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/Liste-Mouser-Tonwelt-TG288.xlsx
+++ b/exports/Liste-Mouser-Tonwelt-TG288.xlsx
@@ -2239,7 +2239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2293,103 +2293,103 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Cellule n°1 - carte à ressort d'antenne (tourGuide AIR probable)</t>
+          <t>Cellule GM 303556</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>JHY632570</t>
+          <t>GM 303556</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>3,7 V · 1300 mAh · 4,81 Wh · 6,3 × 25 × 70 mm</t>
+          <t>3,7 V | 650 mAh | 3,0 x 35 x 56 mm | 2024-03-22</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Chercher : LiPo 3,7 V, 1200-1500 mAh, épaisseur ≤ 6,5 mm, avec circuit de protection et connecteur</t>
+          <t>Chercher le code de taille 303556, ou le plus proche en 3,7 V 600 a 700 mAh, epaisseur 3 mm</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=LiPo+1300mAh+3.7V</t>
+          <t>https://www.mouser.fr/c/?q=LiPo+650mAh+3.7V</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Cellule n°2 - carte Eco 2.0 (supraGuide ECO)</t>
+          <t>Cellule JHY632570, carte a ressort d'antenne</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>sans référence</t>
+          <t>JHY632570</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>3,87 V · 1000 mAh · dimensions à mesurer</t>
+          <t>3,7 V | 1300 mAh | 4,81 Wh | 6,3 x 25 x 70 mm | 2023-01-03</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Attention : 3,87 V = LiPo HAUTE TENSION (charge 4,35 V). Le filtre Mouser ne propose que du 3,7 V : équivalent peu probable en catalogue</t>
+          <t>Chercher le code 632570, ou 1200 a 1500 mAh en 3,7 V, epaisseur 6,5 mm maximum</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=LiPo+1000mAh</t>
+          <t>https://www.mouser.fr/c/?q=LiPo+1300mAh+3.7V</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Cellule n°4</t>
+          <t>Cellule SL5022243</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>LIDIO 355485</t>
+          <t>SL5022243, lot 01536</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>3,8 V · 2500 mAh · 9,5 Wh · 3,5 × 54 × 85 mm</t>
+          <t>3,7 V | 450 mAh | code non decodable avec certitude</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Attention : 3,8 V = haute tension également. Chercher 2000-2600 mAh, épaisseur ≤ 4 mm</t>
+          <t>Mesurer la cellule au pied a coulisse avant toute recherche : le marquage ne donne pas le gabarit</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>https://www.mouser.fr/c/?q=LiPo+2500mAh</t>
+          <t>https://www.mouser.fr/c/?q=LiPo+450mAh+3.7V</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Cellule n°3</t>
+          <t>Cellule LIDIO 355485</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>illisible sur la photo</t>
+          <t>LIDIO 355485</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>3,8 V à confirmer</t>
+          <t>3,8 V | 2500 mAh | 9,5 Wh | 3,5 x 54 x 85 mm | 2020-10</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Refaire une photo nette du marquage avant toute recherche</t>
+          <t>Attention : 3,8 V est une cellule haute tension, charge 4,35 V. Introuvable en catalogue generaliste : OEM ou fabrication sur mesure</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2398,258 +2398,285 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Cellule de la carte Eco 2.0</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>sans reference</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>3,87 V | 1000 mAh | dimensions a mesurer</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Attention : haute tension egalement. Meme conclusion : OEM ou fabrication sur mesure</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Ou chercher un equivalent, site par site</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Quoi</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Pourquoi</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lien</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>DigiKey</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Jauch Quartz, serie LP</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Le meilleur equivalent industriel. Meme convention de code a six chiffres, vendu avec circuit de protection et fils (PCM + 2 WIRES 50MM). Tension 3,7 V, charge 4,20 V. Non distribue par Mouser.</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>https://www.digikey.com/en/product-highlight/j/jauch-quartz/lithium-polymer-batteries</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>DigiKey</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Exemple : LP503562JU</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Format 5,0 x 35 x 62 mm, avec PCM et fils. Sert de modele pour comprendre la designation.</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>https://www.digikey.com/en/products/detail/jauch-quartz/LP503562JU/9560989</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>DigiKey</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Exemple : LP561836JU</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Format 5,6 x 18 x 36 mm, 350 mAh, avec PCM et fils.</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>https://www.digikey.com/en/products/detail/jauch-quartz/LP561836JU-PCM-2-WIRES-50MM/9560979</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>DigiKey</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Catalogue packs lithium polymere</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>A filtrer par capacite et dimensions.</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>https://www.digikey.com/en/products/filter/battery-packs/lithium-polymer/89</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>EEMB (direct ou Amazon.fr)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Cellules poche a code de taille</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Le plus proche de vos cellules OEM : meme logique de code (602835, 603449, 103395), livrees avec connecteur JST et circuit de protection. Fabricant chinois etabli, vendu au detail en Europe.</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>https://www.eemb.com/categories-55</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>TYVA Energie (France)</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Fabrication sur mesure</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Si aucun format standard ne convient, ou pour une cellule haute tension introuvable en catalogue.</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>https://tyva-energie.com/en/custom-lithium-battery-manufacturer/</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Mouser</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Packs LiPo 3,7 V</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Catalogue generaliste, sans recherche par code de taille. Ne propose que du 3,7 V.</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>https://www.mouser.fr/c/?q=3.7V+Lipo+Battery</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Les cinq critères d'un équivalent - aucun n'est facultatif</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>1. Dimensions</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Épaisseur × largeur × longueur MESURÉES au pied à coulisse - le code à six chiffres est une convention, pas une garantie</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>2. Capacité</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>En mAh. Une capacité supérieure allonge l'autonomie mais souvent l'épaisseur aussi</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>3. Tension nominale</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Attention : LE CRITÈRE CRITIQUE. 3,7 V (charge 4,20 V) et 3,8/3,87 V (charge 4,35 V) ne sont PAS interchangeables. Une 3,7 V dans un chargeur 4,35 V est en surcharge permanente : elle chauffe et gonfle</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>4. Circuit de protection</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Vos cellules en ont un, visible sous le kapton jaune. Une cellule nue sans protection est dangereuse dans cet appareil</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>5. Connecteur et POLARITÉ</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>JST 2 points. La polarité n'est pas normalisée sur les cellules chinoises : vérifier au voltmètre AVANT de brancher, sous peine de détruire la carte</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Sécurité : Sécurité : une poche lithium gonflée ou en surchauffe est un risque d'incendie. Ne pas la percer, ne pas la plier, ne pas continuer à la charger. La sortir de l'appareil, la placer dans un contenant ininflammable, la faire reprendre en déchet.</t>
         </is>
@@ -2658,25 +2685,25 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B26:E26"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B22:E22"/>
-    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
